--- a/aani_master.xlsx
+++ b/aani_master.xlsx
@@ -636,7 +636,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C5"/>
+  <dimension ref="A1:D5"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -648,6 +648,9 @@
       <c r="C1" t="str">
         <v>Weeks</v>
       </c>
+      <c r="D1" t="str">
+        <v>Description</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2">
@@ -659,6 +662,9 @@
       <c r="C2">
         <v>3</v>
       </c>
+      <c r="D2" t="str">
+        <v>Documentation: NDA, SOW, MSA and Functional Cover Page signed, and the invoice issued.</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3">
@@ -670,6 +676,9 @@
       <c r="C3">
         <v>3</v>
       </c>
+      <c r="D3" t="str">
+        <v>Certification activities by the assessment team and initial report submission.</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4">
@@ -681,6 +690,9 @@
       <c r="C4">
         <v>4</v>
       </c>
+      <c r="D4" t="str">
+        <v>LFIs fix the findings and the team retests.</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5">
@@ -692,17 +704,20 @@
       <c r="C5">
         <v>2</v>
       </c>
+      <c r="D5" t="str">
+        <v>Closure activities and certification issued.</v>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C5"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D5"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G4"/>
+  <dimension ref="A1:H5"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -725,6 +740,9 @@
       </c>
       <c r="G1" t="str">
         <v>Body</v>
+      </c>
+      <c r="H1" t="str">
+        <v>Trigger</v>
       </c>
     </row>
     <row r="2" xml:space="preserve">
@@ -754,6 +772,9 @@
 Regards,
 Prateek</v>
       </c>
+      <c r="H2" t="str">
+        <v/>
+      </c>
     </row>
     <row r="3" xml:space="preserve">
       <c r="A3" t="str">
@@ -782,6 +803,9 @@
 Regards,
 Prateek</v>
       </c>
+      <c r="H3" t="str">
+        <v/>
+      </c>
     </row>
     <row r="4" xml:space="preserve">
       <c r="A4" t="str">
@@ -810,10 +834,48 @@
 Regards,
 Prateek</v>
       </c>
+      <c r="H4" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="5" xml:space="preserve">
+      <c r="A5" t="str">
+        <v>Create Jira project (certification team)</v>
+      </c>
+      <c r="B5">
+        <v>1</v>
+      </c>
+      <c r="C5" t="str">
+        <v>Certification team</v>
+      </c>
+      <c r="D5">
+        <v>2</v>
+      </c>
+      <c r="E5" t="str">
+        <v/>
+      </c>
+      <c r="F5" t="str">
+        <v>AANI – Create Jira project – {LFI}</v>
+      </c>
+      <c r="G5" t="str" xml:space="preserve">
+        <v xml:space="preserve">Hi team,
+The Functional Cover Page has been received from {LFI}. Please create the Jira project.
+LFI: {LFI}
+Persona: {persona}
+Wave: {wave}
+Batch: {batch}
+Certification fee: {fee}
+Onboarding window: {start} – {end}
+Regards,
+Prateek</v>
+      </c>
+      <c r="H5" t="str">
+        <v>Jira project needed</v>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:G4"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:H5"/>
   </ignoredErrors>
 </worksheet>
 </file>